--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,37 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134954926</v>
+        <v>135251531</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448320</v>
+        <v>448304</v>
       </c>
       <c r="R3" t="n">
-        <v>6753685</v>
+        <v>6753683</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +907,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134954999</v>
+        <v>135252072</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448318</v>
+        <v>448314</v>
       </c>
       <c r="R4" t="n">
-        <v>6753726</v>
+        <v>6753714</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +981,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,6 +1020,238 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134954926</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>448320</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6753685</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134954999</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448318</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6753726</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,57 +1023,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134954926</v>
+        <v>135252034</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vällbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448320</v>
+        <v>448329</v>
       </c>
       <c r="R5" t="n">
-        <v>6753685</v>
+        <v>6753704</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1097,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,6 +1121,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134954999</v>
+        <v>134954926</v>
       </c>
       <c r="B6" t="n">
         <v>79131</v>
@@ -1169,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1183,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448318</v>
+        <v>448320</v>
       </c>
       <c r="R6" t="n">
-        <v>6753726</v>
+        <v>6753685</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1218,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1253,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134954999</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448318</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753726</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955028</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251531</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252072</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252034</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134954926</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,8 +1399,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134954999</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134955028</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135251531</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135252072</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135252034</v>
       </c>
       <c r="B5" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>134954926</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>134954999</v>
       </c>
       <c r="B7" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135251531</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135252072</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,37 +801,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134954926</v>
+        <v>135251531</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448320</v>
+        <v>448304</v>
       </c>
       <c r="R3" t="n">
-        <v>6753685</v>
+        <v>6753683</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,43 +916,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134954926</t>
+          <t>https://artportalen.se/Sighting/135251531</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134954999</v>
+        <v>135252072</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448318</v>
+        <v>448314</v>
       </c>
       <c r="R4" t="n">
-        <v>6753726</v>
+        <v>6753714</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +996,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,6 +1036,370 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252072</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135252034</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>448329</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6753704</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252034</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134954926</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448320</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6753685</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134954926</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134954999</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448318</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753726</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134954999</t>
         </is>
@@ -1046,6 +1410,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134955028</v>
+        <v>135998295</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vällbäcken, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448318</v>
+        <v>448316</v>
       </c>
       <c r="R2" t="n">
-        <v>6753726</v>
+        <v>6753756</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,60 +786,51 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134955028</t>
+          <t>https://artportalen.se/Sighting/135998295</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135251531</v>
+        <v>135998296</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>91834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vällbäcken, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448304</v>
+        <v>448300</v>
       </c>
       <c r="R3" t="n">
-        <v>6753683</v>
+        <v>6753762</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135251531</t>
+          <t>https://artportalen.se/Sighting/135998296</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135252072</v>
+        <v>134955028</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448314</v>
+        <v>448318</v>
       </c>
       <c r="R4" t="n">
-        <v>6753714</v>
+        <v>6753726</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,60 +1019,60 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252072</t>
+          <t>https://artportalen.se/Sighting/134955028</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135252034</v>
+        <v>135251531</v>
       </c>
       <c r="B5" t="n">
-        <v>8461</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vällbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448329</v>
+        <v>448304</v>
       </c>
       <c r="R5" t="n">
-        <v>6753704</v>
+        <v>6753683</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1122,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1159,43 +1140,43 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135252034</t>
+          <t>https://artportalen.se/Sighting/135251531</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134954926</v>
+        <v>135252072</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1209,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448320</v>
+        <v>448314</v>
       </c>
       <c r="R6" t="n">
-        <v>6753685</v>
+        <v>6753714</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1220,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,63 +1261,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134954926</t>
+          <t>https://artportalen.se/Sighting/135252072</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134954999</v>
+        <v>135998297</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällbäcken, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448318</v>
+        <v>448317</v>
       </c>
       <c r="R7" t="n">
-        <v>6753726</v>
+        <v>6753717</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,22 +1332,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1373,595 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135998297</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135998298</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>448327</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6753704</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998298</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135252034</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448329</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6753704</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252034</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134954926</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>448320</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6753685</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134954926</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134954999</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vällbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>448318</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6753726</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134954999</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135998299</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>448336</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6753678</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998299</t>
         </is>
       </c>
     </row>
@@ -1413,6 +1973,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998295</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998296</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>135998297</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135998298</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135998299</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998295</v>
       </c>
       <c r="B2" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998296</v>
       </c>
       <c r="B3" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998295</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998296</v>
       </c>
       <c r="B3" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>135998297</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135998298</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135998299</v>
       </c>
       <c r="B12" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998295</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998296</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>135998297</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135998298</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135998299</v>
       </c>
       <c r="B12" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29123-2026 artfynd.xlsx
+++ b/artfynd/A 29123-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998295</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998296</v>
       </c>
       <c r="B3" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>135998297</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>135998298</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>135998299</v>
       </c>
       <c r="B12" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
